--- a/data/raw/2026-04-29_HV.xlsx
+++ b/data/raw/2026-04-29_HV.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>M F Poon</t>
+          <t>M L Yeung</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>M F Poon</t>
+          <t>J Orman</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>M F Poon</t>
+          <t>E Brown</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>M F Poon</t>
+          <t>K Teetan</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>M F Poon</t>
+          <t>K C Leung</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>M F Poon</t>
+          <t>K C Leung</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>M F Poon</t>
+          <t>K C Leung</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -7484,23 +7484,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>105</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3" t="n">
         <v>46</v>
       </c>
       <c r="G3" t="n">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -7519,11 +7519,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D4" t="n">
         <v>31</v>
@@ -7535,7 +7535,7 @@
         <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -7564,13 +7564,13 @@
         <v>39</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" t="n">
         <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -7599,13 +7599,13 @@
         <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -7624,23 +7624,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7" t="n">
         <v>49</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -7666,16 +7666,16 @@
         <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E8" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -7701,16 +7701,16 @@
         <v>22</v>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E9" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F9" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -7729,23 +7729,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F10" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G10" t="n">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -7764,14 +7764,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E11" t="n">
         <v>35</v>
@@ -7780,7 +7780,7 @@
         <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>29</v>
       </c>
       <c r="G12" t="n">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -7844,13 +7844,13 @@
         <v>22</v>
       </c>
       <c r="E13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" t="n">
         <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -7879,13 +7879,13 @@
         <v>27</v>
       </c>
       <c r="E14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F14" t="n">
         <v>35</v>
       </c>
       <c r="G14" t="n">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>26</v>
       </c>
       <c r="G15" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -7987,10 +7987,10 @@
         <v>14</v>
       </c>
       <c r="F17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -8013,19 +8013,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D18" t="n">
+        <v>20</v>
+      </c>
+      <c r="E18" t="n">
         <v>15</v>
       </c>
-      <c r="E18" t="n">
-        <v>6</v>
-      </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="G18" t="n">
-        <v>101</v>
+        <v>348</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -8044,23 +8044,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E19" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F19" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -8079,23 +8079,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E20" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F20" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="G20" t="n">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -8114,23 +8114,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G21" t="n">
-        <v>169</v>
+        <v>327</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -8149,23 +8149,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>345</v>
+        <v>112</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -8184,23 +8184,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>325</v>
+        <v>57</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -8219,23 +8219,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
         <v>6</v>
       </c>
-      <c r="F24" t="n">
-        <v>5</v>
-      </c>
       <c r="G24" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -8254,23 +8254,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="n">
         <v>2</v>
       </c>
-      <c r="F25" t="n">
-        <v>7</v>
-      </c>
       <c r="G25" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -8289,23 +8289,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -8324,23 +8324,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -8359,23 +8359,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G28" t="n">
-        <v>7</v>
+        <v>171</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -8394,23 +8394,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G29" t="n">
-        <v>7</v>
+        <v>142</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -8429,23 +8429,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -8477,10 +8477,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -8538,19 +8538,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -8573,19 +8573,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -8604,23 +8604,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -8639,23 +8639,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
         <v>9</v>
-      </c>
-      <c r="D36" t="n">
-        <v>7</v>
-      </c>
-      <c r="E36" t="n">
-        <v>13</v>
-      </c>
-      <c r="F36" t="n">
-        <v>4</v>
-      </c>
-      <c r="G36" t="n">
-        <v>99</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -8674,23 +8674,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -8709,11 +8709,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -8722,10 +8722,10 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G38" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -8748,19 +8748,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -8786,16 +8786,16 @@
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>132</v>
+        <v>1</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -8824,13 +8824,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -8853,19 +8853,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -8888,19 +8888,19 @@
         </is>
       </c>
       <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
         <v>1</v>
       </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -8923,19 +8923,19 @@
         </is>
       </c>
       <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
         <v>1</v>
       </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -8958,19 +8958,19 @@
         </is>
       </c>
       <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
         <v>1</v>
       </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -8996,16 +8996,16 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -9034,13 +9034,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
         <v>1</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
-        <v>2</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -9228,10 +9228,10 @@
         <v>31</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -9255,13 +9255,13 @@
         <v>41</v>
       </c>
       <c r="E4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -9291,7 +9291,7 @@
         <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -9305,23 +9305,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6" t="n">
         <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -9335,11 +9335,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" t="n">
         <v>50</v>
@@ -9351,7 +9351,7 @@
         <v>32</v>
       </c>
       <c r="G7" t="n">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>50</v>
       </c>
       <c r="D8" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E8" t="n">
         <v>33</v>
@@ -9381,7 +9381,7 @@
         <v>46</v>
       </c>
       <c r="G8" t="n">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -9411,7 +9411,7 @@
         <v>29</v>
       </c>
       <c r="G9" t="n">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -9429,19 +9429,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" t="n">
         <v>42</v>
       </c>
       <c r="E10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F10" t="n">
         <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -9459,19 +9459,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E11" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G11" t="n">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -9485,23 +9485,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D12" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="E12" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G12" t="n">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -9519,19 +9519,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E13" t="n">
         <v>26</v>
       </c>
       <c r="F13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -9549,19 +9549,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F14" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G14" t="n">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -9575,23 +9575,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E15" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F15" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -9609,19 +9609,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E16" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F16" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G16" t="n">
-        <v>315</v>
+        <v>346</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -9645,13 +9645,13 @@
         <v>27</v>
       </c>
       <c r="E17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G17" t="n">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -9665,11 +9665,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
         <v>24</v>
@@ -9681,7 +9681,7 @@
         <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -9695,23 +9695,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F19" t="n">
         <v>18</v>
       </c>
       <c r="G19" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -9729,19 +9729,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F20" t="n">
         <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>17</v>
       </c>
       <c r="G21" t="n">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -9795,13 +9795,13 @@
         <v>15</v>
       </c>
       <c r="E22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F22" t="n">
         <v>24</v>
       </c>
       <c r="G22" t="n">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>24</v>
       </c>
       <c r="G24" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -9999,10 +9999,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -10011,7 +10011,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -10029,13 +10029,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -10062,16 +10062,16 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -10092,16 +10092,16 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>2</v>
@@ -10155,13 +10155,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -10188,10 +10188,10 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -10218,10 +10218,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -10248,10 +10248,10 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -10278,10 +10278,10 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10596,47 +10596,47 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>pts_22/4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>pts_19/4</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pts_15/4</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pts_12/4</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>pts_8/4</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>pts_6/4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>pts_1/4</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>pts_29/3</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>pts_25/3</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>pts_22/3</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
@@ -10648,368 +10648,406 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Z Purton</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C2" t="n">
-        <v>30.5</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>33.4</v>
+        <v>30.8</v>
       </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G2" t="n">
         <v>48</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>28</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>24</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>18</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>28</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>40</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>18</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>22</v>
-      </c>
-      <c r="M2" t="n">
-        <v>44</v>
-      </c>
-      <c r="N2" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J Moreira</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.4</v>
+        <v>36</v>
       </c>
       <c r="C3" t="n">
-        <v>20.3</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>27.5</v>
+        <v>16.8</v>
       </c>
       <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
+        <v>22</v>
+      </c>
+      <c r="I3" t="n">
         <v>28</v>
       </c>
-      <c r="G3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H3" t="n">
-        <v>10</v>
-      </c>
-      <c r="I3" t="n">
-        <v>54</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>24</v>
+      </c>
+      <c r="L3" t="n">
+        <v>30</v>
+      </c>
+      <c r="M3" t="n">
+        <v>16</v>
+      </c>
+      <c r="N3" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E Brown</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>22</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>48</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H Bowman</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>16.6</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>18.6</v>
+        <v>6.6</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>28</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" t="n">
         <v>4</v>
       </c>
-      <c r="I5" t="n">
-        <v>24</v>
-      </c>
-      <c r="J5" t="n">
-        <v>30</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>16</v>
       </c>
-      <c r="L5" t="n">
-        <v>18</v>
-      </c>
-      <c r="M5" t="n">
-        <v>36</v>
-      </c>
       <c r="N5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H Y Yuen</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.5</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>11.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>16</v>
+      </c>
       <c r="H6" t="n">
-        <v>34</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>20</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>18</v>
+      </c>
+      <c r="N6" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A Atzeni</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.8</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>15.5</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>12</v>
       </c>
-      <c r="F7" t="n">
-        <v>28</v>
-      </c>
-      <c r="G7" t="n">
-        <v>12</v>
-      </c>
-      <c r="H7" t="n">
-        <v>18</v>
-      </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J7" t="n">
         <v>22</v>
       </c>
       <c r="K7" t="n">
+        <v>20</v>
+      </c>
+      <c r="L7" t="n">
+        <v>18</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7" t="n">
         <v>22</v>
-      </c>
-      <c r="L7" t="n">
-        <v>30</v>
-      </c>
-      <c r="M7" t="n">
-        <v>8</v>
-      </c>
-      <c r="N7" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A Badel</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.8</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>28</v>
+      </c>
+      <c r="G8" t="n">
         <v>24</v>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
         <v>12</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>8</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>40</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>24</v>
-      </c>
-      <c r="M8" t="n">
-        <v>18</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H Bentley</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>8.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J9" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="L9" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C L Chau</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>7.2</v>
+        <v>9.5</v>
       </c>
       <c r="E10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>12</v>
@@ -11018,222 +11056,196 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K Teetan</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11.6</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>5.6</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" t="n">
         <v>4</v>
       </c>
-      <c r="H11" t="n">
-        <v>12</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K11" t="n">
-        <v>10</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>8</v>
-      </c>
       <c r="N11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B Avdulla</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>13.8</v>
+        <v>8.9</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" t="n">
         <v>16</v>
       </c>
-      <c r="G12" t="n">
-        <v>18</v>
-      </c>
-      <c r="H12" t="n">
-        <v>34</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J Orman</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>6</v>
-      </c>
-      <c r="I13" t="n">
-        <v>8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>12</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4</v>
-      </c>
-      <c r="L13" t="n">
-        <v>12</v>
-      </c>
-      <c r="M13" t="n">
-        <v>16</v>
-      </c>
-      <c r="N13" t="n">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K C Leung</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>11.3</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>6</v>
-      </c>
-      <c r="I14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>12</v>
-      </c>
-      <c r="K14" t="n">
-        <v>12</v>
-      </c>
-      <c r="L14" t="n">
-        <v>6</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>22</v>
-      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M F Poon</t>
+          <t>B Avdulla</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.8</v>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H15" t="n">
+        <v>18</v>
+      </c>
+      <c r="I15" t="n">
+        <v>34</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>4</v>
       </c>
-      <c r="G15" t="n">
-        <v>6</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
       <c r="L15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>10</v>
@@ -11242,107 +11254,109 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C Y Ho</t>
+          <t>J Orman</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="C16" t="n">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>15.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
         <v>6</v>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M16" t="n">
         <v>12</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Y L Chung</t>
+          <t>R Kingscote</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>6</v>
       </c>
-      <c r="D17" t="n">
+      <c r="I17" t="n">
         <v>6</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>30</v>
+      </c>
+      <c r="M17" t="n">
         <v>18</v>
       </c>
-      <c r="H17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" t="n">
-        <v>30</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>6</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L Ferraris</t>
+          <t>K C Leung</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>7.3</v>
       </c>
       <c r="D18" t="n">
-        <v>10.9</v>
+        <v>11.3</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -11350,70 +11364,68 @@
       <c r="F18" t="n">
         <v>0</v>
       </c>
-      <c r="G18" t="n">
-        <v>12</v>
-      </c>
-      <c r="H18" t="n">
-        <v>16</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>6</v>
+      </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
         <v>12</v>
       </c>
       <c r="L18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R Kingscote</t>
+          <t>M L Yeung</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="C19" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="D19" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -11422,30 +11434,30 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M L Yeung</t>
+          <t>E C W Wong</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>6.1</v>
+        <v>7.1</v>
       </c>
       <c r="E20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
         <v>6</v>
       </c>
-      <c r="H20" t="n">
-        <v>14</v>
-      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -11453,38 +11465,38 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>6</v>
       </c>
-      <c r="L20" t="n">
-        <v>8</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
       <c r="N20" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P N Wong</t>
+          <t>H T Mo</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>6.8</v>
+        <v>1.3</v>
       </c>
       <c r="D21" t="n">
-        <v>6.7</v>
+        <v>1.4</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -11493,13 +11505,13 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -11510,398 +11522,6 @@
       <c r="N21" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>L Hewitson</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="C22" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="D22" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="E22" t="n">
-        <v>6</v>
-      </c>
-      <c r="F22" t="n">
-        <v>12</v>
-      </c>
-      <c r="G22" t="n">
-        <v>10</v>
-      </c>
-      <c r="H22" t="n">
-        <v>6</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>12</v>
-      </c>
-      <c r="N22" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>E C W Wong</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C23" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="D23" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>12</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>6</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>6</v>
-      </c>
-      <c r="M23" t="n">
-        <v>6</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>M Chadwick</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C24" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="D24" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>6</v>
-      </c>
-      <c r="J24" t="n">
-        <v>6</v>
-      </c>
-      <c r="K24" t="n">
-        <v>4</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>6</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>C Lemaire</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>C Williams</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="n">
-        <v>10</v>
-      </c>
-      <c r="D26" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>H T Mo</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>J Collett</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>J McDonald</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="D29" t="n">
-        <v>27</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>M Guyon</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>M Zahra</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>O Murphy</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>12</v>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Y Kawada</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11914,7 +11534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11940,47 +11560,47 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>pts_22/4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>pts_19/4</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pts_15/4</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pts_12/4</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>pts_8/4</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>pts_6/4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>pts_1/4</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>pts_29/3</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>pts_25/3</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>pts_22/3</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
@@ -11992,735 +11612,735 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J Size</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.4</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>17.2</v>
+        <v>13.4</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
         <v>12</v>
       </c>
       <c r="H2" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N2" t="n">
         <v>14</v>
-      </c>
-      <c r="L2" t="n">
-        <v>18</v>
-      </c>
-      <c r="M2" t="n">
-        <v>14</v>
-      </c>
-      <c r="N2" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C S Shum</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.1</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>9.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J3" t="n">
         <v>12</v>
       </c>
-      <c r="G3" t="n">
-        <v>52</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I3" t="n">
-        <v>12</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M3" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M Newnham</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.6</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>12</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
         <v>18</v>
       </c>
-      <c r="G4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
+        <v>22</v>
+      </c>
+      <c r="J4" t="n">
         <v>12</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>30</v>
-      </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L4" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C Fownes</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
         <v>14</v>
       </c>
-      <c r="C5" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>12.5</v>
-      </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>24</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>22</v>
+      </c>
+      <c r="K5" t="n">
         <v>10</v>
       </c>
-      <c r="F5" t="n">
-        <v>22</v>
-      </c>
-      <c r="G5" t="n">
-        <v>20</v>
-      </c>
-      <c r="H5" t="n">
-        <v>10</v>
-      </c>
-      <c r="I5" t="n">
-        <v>54</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4</v>
-      </c>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A S Cruz</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.4</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>12.6</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" t="n">
         <v>18</v>
       </c>
-      <c r="G6" t="n">
-        <v>22</v>
-      </c>
       <c r="H6" t="n">
+        <v>48</v>
+      </c>
+      <c r="I6" t="n">
         <v>12</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
+        <v>28</v>
+      </c>
+      <c r="K6" t="n">
+        <v>16</v>
+      </c>
+      <c r="L6" t="n">
+        <v>20</v>
+      </c>
+      <c r="M6" t="n">
+        <v>14</v>
+      </c>
+      <c r="N6" t="n">
         <v>18</v>
-      </c>
-      <c r="J6" t="n">
-        <v>12</v>
-      </c>
-      <c r="K6" t="n">
-        <v>24</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>12</v>
-      </c>
-      <c r="N6" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D A Hayes</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="C7" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>24</v>
+      </c>
+      <c r="G7" t="n">
+        <v>18</v>
+      </c>
+      <c r="H7" t="n">
         <v>12</v>
       </c>
-      <c r="F7" t="n">
+      <c r="I7" t="n">
+        <v>52</v>
+      </c>
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="G7" t="n">
-        <v>24</v>
-      </c>
-      <c r="H7" t="n">
-        <v>26</v>
-      </c>
-      <c r="I7" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>12</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
         <v>4</v>
       </c>
-      <c r="L7" t="n">
-        <v>14</v>
-      </c>
-      <c r="M7" t="n">
-        <v>12</v>
-      </c>
       <c r="N7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K W Lui</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12.6</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>10</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N8" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P F Yiu</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>12.9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
         <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F C Lor</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11.6</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>9.1</v>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="n">
         <v>12</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>22</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" t="n">
-        <v>6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>12</v>
-      </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="L10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="N10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D Eustace</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10.4</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>9.4</v>
+        <v>15.2</v>
       </c>
       <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
         <v>12</v>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H11" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K11" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="M11" t="n">
         <v>6</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D J Whyte</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10.4</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="H12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" t="n">
+        <v>16</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>12</v>
       </c>
-      <c r="I12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J12" t="n">
-        <v>34</v>
-      </c>
-      <c r="K12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L12" t="n">
-        <v>10</v>
-      </c>
       <c r="M12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K L Man</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>9.5</v>
+        <v>14.1</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I13" t="n">
+        <v>20</v>
+      </c>
+      <c r="J13" t="n">
         <v>10</v>
       </c>
-      <c r="J13" t="n">
-        <v>28</v>
-      </c>
       <c r="K13" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N13" t="n">
         <v>10</v>
-      </c>
-      <c r="M13" t="n">
-        <v>12</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J Richards</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
         <v>6</v>
       </c>
-      <c r="E14" t="n">
-        <v>24</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
       <c r="G14" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H14" t="n">
+        <v>22</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
         <v>4</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
+        <v>6</v>
+      </c>
+      <c r="L14" t="n">
         <v>12</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>4</v>
       </c>
-      <c r="M14" t="n">
-        <v>6</v>
-      </c>
       <c r="N14" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>W Y So</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>8.9</v>
+        <v>5.4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>W K Mo</t>
+          <t>P F Yiu</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6.8</v>
+        <v>14.4</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>10.8</v>
       </c>
       <c r="D16" t="n">
-        <v>9.699999999999999</v>
+        <v>12.9</v>
       </c>
       <c r="E16" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F16" t="n">
         <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="J16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M16" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C H Yip</t>
+          <t>W Y So</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="C17" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="D17" t="n">
-        <v>6.5</v>
+        <v>8.9</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
+        <v>18</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>18</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>18</v>
+      </c>
+      <c r="L17" t="n">
         <v>4</v>
       </c>
-      <c r="H17" t="n">
-        <v>16</v>
-      </c>
-      <c r="I17" t="n">
-        <v>10</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>24</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -12733,20 +12353,20 @@
         <v>6.4</v>
       </c>
       <c r="C18" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D18" t="n">
         <v>7.7</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
         <v>8</v>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
@@ -12754,19 +12374,19 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>12</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>18</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>10</v>
-      </c>
-      <c r="N18" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -12776,89 +12396,89 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="C19" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
+        <v>18</v>
+      </c>
+      <c r="F19" t="n">
         <v>8</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>4</v>
       </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
       <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>6</v>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>12</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>6</v>
-      </c>
-      <c r="L19" t="n">
-        <v>4</v>
       </c>
       <c r="M19" t="n">
         <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P C Ng</t>
+          <t>C H Yip</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="D20" t="n">
-        <v>11.2</v>
+        <v>6.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>6</v>
       </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -12868,20 +12488,20 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="D21" t="n">
         <v>5.4</v>
       </c>
       <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
         <v>18</v>
       </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
@@ -12889,22 +12509,22 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
         <v>8</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>6</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>12</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>6</v>
-      </c>
-      <c r="N21" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -12917,17 +12537,17 @@
         <v>3.6</v>
       </c>
       <c r="C22" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="D22" t="n">
         <v>4.9</v>
       </c>
       <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
         <v>8</v>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
@@ -12938,13 +12558,13 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>12</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>16</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -12956,20 +12576,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Y S Tsui</t>
+          <t>P C Ng</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="C23" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>5.1</v>
+        <v>11.2</v>
       </c>
       <c r="E23" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -12981,283 +12601,23 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A Fabre</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>12</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>D A O'Brien</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>H Eustace</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>H Sugiyama</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>H Take</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>K Burke</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>N Hori</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>13</v>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>R Takei</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>T Takano</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>T Tezuka</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13270,7 +12630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13342,22 +12702,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D3" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="E3" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F3" t="n">
         <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
@@ -13367,16 +12727,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D4" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F4" t="n">
         <v>12</v>
@@ -13392,13 +12752,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E5" t="n">
         <v>37</v>
@@ -13417,7 +12777,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="C6" t="n">
         <v>35</v>
@@ -13426,7 +12786,7 @@
         <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" t="n">
         <v>7</v>
@@ -13442,13 +12802,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="C7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E7" t="n">
         <v>25</v>
@@ -13463,76 +12823,76 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H Bentley</t>
+          <t>C Y Ho</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="C8" t="n">
         <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L Ferraris</t>
+          <t>H Bentley</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="C9" t="n">
         <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E9" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="n">
         <v>6</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C Y Ho</t>
+          <t>L Ferraris</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E10" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -13542,13 +12902,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E11" t="n">
         <v>19</v>
@@ -13567,7 +12927,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C12" t="n">
         <v>25</v>
@@ -13592,7 +12952,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C13" t="n">
         <v>23</v>
@@ -13617,7 +12977,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C14" t="n">
         <v>23</v>
@@ -13626,7 +12986,7 @@
         <v>75</v>
       </c>
       <c r="E14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F14" t="n">
         <v>3</v>
@@ -13642,7 +13002,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C15" t="n">
         <v>20</v>
@@ -13651,7 +13011,7 @@
         <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F15" t="n">
         <v>4</v>
@@ -13667,7 +13027,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C16" t="n">
         <v>20</v>
@@ -13692,7 +13052,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C17" t="n">
         <v>19</v>
@@ -13717,7 +13077,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C18" t="n">
         <v>16</v>
@@ -13738,48 +13098,48 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J McDonald</t>
+          <t>B Avdulla</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>101</v>
+        <v>329</v>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="E19" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B Avdulla</t>
+          <t>R Kingscote</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="C20" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -13788,48 +13148,48 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M Guyon</t>
+          <t>M Chadwick</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>169</v>
+        <v>327</v>
       </c>
       <c r="C21" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E21" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R Kingscote</t>
+          <t>P N Wong</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>345</v>
+        <v>112</v>
       </c>
       <c r="C22" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E22" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -13838,23 +13198,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M Chadwick</t>
+          <t>J Moreira</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>325</v>
+        <v>57</v>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E23" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="G23" t="n">
         <v>2</v>
@@ -13863,23 +13223,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P N Wong</t>
+          <t>H Y Yuen</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -13888,123 +13248,123 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J Moreira</t>
+          <t>H T Mo</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>47</v>
+        <v>104</v>
       </c>
       <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
         <v>8</v>
       </c>
-      <c r="D25" t="n">
-        <v>18</v>
-      </c>
       <c r="E25" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>H Y Yuen</t>
+          <t>E Brown</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>H T Mo</t>
+          <t>J McDonald</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E Brown</t>
+          <t>M Guyon</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>171</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C Williams</t>
+          <t>D B McMonagle</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>142</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
+        <v>31</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="n">
         <v>2</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -14013,23 +13373,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C Lemaire</t>
+          <t>H Doyle</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -14038,48 +13398,48 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>O Murphy</t>
+          <t>R Moore</t>
         </is>
       </c>
       <c r="B31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C31" t="n">
         <v>2</v>
       </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>D B McMonagle</t>
+          <t>W Buick</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>142</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -14088,20 +13448,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>H Doyle</t>
+          <t>K De Melo</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
         <v>3</v>
@@ -14113,48 +13473,48 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>R Moore</t>
+          <t>D Probert</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10</v>
+        <v>132</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>W Buick</t>
+          <t>C Williams</t>
         </is>
       </c>
       <c r="B35" t="n">
+        <v>11</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
         <v>4</v>
       </c>
-      <c r="C35" t="n">
+      <c r="E35" t="n">
         <v>1</v>
       </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -14163,23 +13523,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>K De Melo</t>
+          <t>C Soumillon</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -14188,17 +13548,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>D Probert</t>
+          <t>C Lemaire</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>132</v>
+        <v>9</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -14213,17 +13573,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C Soumillon</t>
+          <t>M Barzalona</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -14238,11 +13598,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>M Barzalona</t>
+          <t>C Demuro</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -14263,11 +13623,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C Demuro</t>
+          <t>R King</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -14288,11 +13648,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>R King</t>
+          <t>U Rispoli</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -14313,11 +13673,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>U Rispoli</t>
+          <t>K Yokoyama</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -14338,11 +13698,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>K Yokoyama</t>
+          <t>M Zahra</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -14363,7 +13723,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>K Miura</t>
+          <t>Y Kawada</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -14376,10 +13736,10 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -14388,11 +13748,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>T Marquand</t>
+          <t>J Collett</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -14413,7 +13773,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A Pouchin</t>
+          <t>K Miura</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -14432,6 +13792,81 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>O Murphy</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T Marquand</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>A Pouchin</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14446,7 +13881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14518,19 +13953,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="C3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E3" t="n">
         <v>56</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
         <v>18</v>
@@ -14543,16 +13978,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="C4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F4" t="n">
         <v>15</v>
@@ -14568,22 +14003,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C5" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -14593,22 +14028,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="C6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
         <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -14618,19 +14053,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="C7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E7" t="n">
         <v>52</v>
       </c>
       <c r="F7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
         <v>14</v>
@@ -14643,16 +14078,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="C8" t="n">
         <v>41</v>
       </c>
       <c r="D8" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E8" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F8" t="n">
         <v>9</v>
@@ -14668,13 +14103,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E9" t="n">
         <v>32</v>
@@ -14693,16 +14128,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="C10" t="n">
         <v>32</v>
       </c>
       <c r="D10" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F10" t="n">
         <v>11</v>
@@ -14714,51 +14149,51 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K L Man</t>
+          <t>P F Yiu</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="C11" t="n">
         <v>31</v>
       </c>
       <c r="D11" t="n">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="E11" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P F Yiu</t>
+          <t>K L Man</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="C12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="E12" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -14768,16 +14203,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="C13" t="n">
         <v>29</v>
       </c>
       <c r="D13" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
@@ -14793,13 +14228,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C14" t="n">
         <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E14" t="n">
         <v>32</v>
@@ -14818,16 +14253,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F15" t="n">
         <v>7</v>
@@ -14843,13 +14278,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C16" t="n">
         <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E16" t="n">
         <v>20</v>
@@ -14868,7 +14303,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C17" t="n">
         <v>20</v>
@@ -14893,13 +14328,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E18" t="n">
         <v>20</v>
@@ -14918,16 +14353,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D19" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F19" t="n">
         <v>6</v>
@@ -14943,13 +14378,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C20" t="n">
         <v>17</v>
       </c>
       <c r="D20" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E20" t="n">
         <v>17</v>
@@ -14968,7 +14403,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C21" t="n">
         <v>16</v>
@@ -14993,7 +14428,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C22" t="n">
         <v>15</v>
@@ -15018,7 +14453,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C23" t="n">
         <v>14</v>
@@ -15043,7 +14478,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C24" t="n">
         <v>13</v>
@@ -15055,7 +14490,7 @@
         <v>12</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
         <v>4</v>
@@ -15068,19 +14503,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -15114,7 +14549,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>M Botti</t>
+          <t>T Tezuka</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -15139,7 +14574,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>H Uemura</t>
+          <t>M Botti</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -15164,7 +14599,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Y Ikee</t>
+          <t>H Uemura</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -15189,7 +14624,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A P O'Brien</t>
+          <t>N Hori</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -15199,7 +14634,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -15214,17 +14649,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>K Mori</t>
+          <t>H Eustace</t>
         </is>
       </c>
       <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
         <v>1</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -15239,7 +14674,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>H Tanaka</t>
+          <t>Y Ikee</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -15249,7 +14684,7 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -15264,7 +14699,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>N Hori</t>
+          <t>T Takano</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -15277,10 +14712,10 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -15289,7 +14724,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C Hills</t>
+          <t>H Sugiyama</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -15314,11 +14749,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A M Balding</t>
+          <t>A P O'Brien</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -15339,11 +14774,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>J P O'Brien</t>
+          <t>H Take</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -15364,7 +14799,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>H Eustace</t>
+          <t>D A O'Brien</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -15389,7 +14824,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Y Barberot</t>
+          <t>K Mori</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -15414,7 +14849,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>R Takei</t>
+          <t>H Tanaka</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -15439,7 +14874,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Y Shikato</t>
+          <t>C Hills</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -15458,6 +14893,156 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>A M Balding</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>J P O'Brien</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>K Burke</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Y Barberot</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>R Takei</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Y Shikato</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16463,7 +16048,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>M F Poon</t>
+          <t>M L Yeung</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -16952,7 +16537,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>M F Poon</t>
+          <t>J Orman</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -18448,7 +18033,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M F Poon</t>
+          <t>E Brown</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19600,7 +19185,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>M F Poon</t>
+          <t>K Teetan</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -20696,7 +20281,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>M F Poon</t>
+          <t>K C Leung</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
